--- a/huge数据对比/3mz-vs-Crazycong.xlsx
+++ b/huge数据对比/3mz-vs-Crazycong.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\huge数据对比\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD208C57-C502-4151-9EB6-0AF13FC6A0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3673E81-F16C-47A5-AC56-0AE910FBF831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -203,6 +203,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -501,11 +504,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,11 +564,11 @@
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
       <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
@@ -624,9 +627,9 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
@@ -685,9 +688,9 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
@@ -756,11 +759,11 @@
       <c r="AB4" s="1"/>
     </row>
     <row r="5" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="1" t="s">
         <v>0</v>
       </c>
@@ -816,11 +819,11 @@
       <c r="AB5" s="1"/>
     </row>
     <row r="6" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="9" t="s">
         <v>22</v>
       </c>
@@ -879,9 +882,9 @@
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="9" t="s">
         <v>4</v>
       </c>
@@ -940,9 +943,9 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="9" t="s">
         <v>23</v>
       </c>
@@ -1011,11 +1014,11 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1071,11 +1074,11 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
       <c r="D10" s="9" t="s">
         <v>22</v>
       </c>
@@ -1134,9 +1137,9 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="9" t="s">
         <v>4</v>
       </c>
@@ -1195,9 +1198,9 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
       <c r="D12" s="9" t="s">
         <v>23</v>
       </c>
@@ -1266,11 +1269,11 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
       <c r="D13" s="9" t="s">
         <v>0</v>
       </c>
@@ -1326,11 +1329,11 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
       <c r="D14" s="9" t="s">
         <v>22</v>
       </c>
@@ -1389,9 +1392,9 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
       <c r="D15" s="9" t="s">
         <v>4</v>
       </c>
@@ -1450,9 +1453,9 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
       <c r="D16" s="9" t="s">
         <v>23</v>
       </c>
@@ -1521,11 +1524,11 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="9" t="s">
         <v>0</v>
       </c>
@@ -1581,11 +1584,11 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
       <c r="D18" s="9" t="s">
         <v>22</v>
       </c>
@@ -1644,9 +1647,9 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
       <c r="D19" s="9" t="s">
         <v>4</v>
       </c>
@@ -1705,9 +1708,9 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
       <c r="D20" s="9" t="s">
         <v>23</v>
       </c>
@@ -1776,11 +1779,11 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
       <c r="D21" s="9" t="s">
         <v>0</v>
       </c>
@@ -1836,11 +1839,11 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
       <c r="D22" s="9" t="s">
         <v>22</v>
       </c>
@@ -1899,9 +1902,9 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
       <c r="D23" s="9" t="s">
         <v>4</v>
       </c>
@@ -1960,9 +1963,9 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
       <c r="D24" s="9" t="s">
         <v>23</v>
       </c>
@@ -2031,11 +2034,11 @@
       <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
       <c r="D25" s="1" t="s">
         <v>0</v>
       </c>
@@ -2091,11 +2094,11 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
       <c r="D26" s="9" t="s">
         <v>22</v>
       </c>
@@ -2154,9 +2157,9 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
       <c r="D27" s="9" t="s">
         <v>25</v>
       </c>
@@ -2185,7 +2188,8 @@
       <c r="L27" s="9">
         <v>22209</v>
       </c>
-      <c r="M27" s="9">
+      <c r="M27" s="10">
+        <f t="shared" si="28"/>
         <v>1540</v>
       </c>
       <c r="N27" s="8">
@@ -2214,9 +2218,9 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
       <c r="D28" s="9" t="s">
         <v>23</v>
       </c>
@@ -2285,9 +2289,9 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -2315,9 +2319,9 @@
       <c r="AB29" s="1"/>
     </row>
     <row r="30" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -2345,9 +2349,9 @@
       <c r="AB30" s="1"/>
     </row>
     <row r="31" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -2375,9 +2379,9 @@
       <c r="AB31" s="1"/>
     </row>
     <row r="32" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="1"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2405,9 +2409,9 @@
       <c r="AB32" s="1"/>
     </row>
     <row r="33" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2435,9 +2439,9 @@
       <c r="AB33" s="1"/>
     </row>
     <row r="34" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2465,9 +2469,9 @@
       <c r="AB34" s="1"/>
     </row>
     <row r="35" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -2495,9 +2499,9 @@
       <c r="AB35" s="1"/>
     </row>
     <row r="36" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
       <c r="D36" s="1"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -2525,9 +2529,9 @@
       <c r="AB36" s="1"/>
     </row>
     <row r="37" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -2555,9 +2559,9 @@
       <c r="AB37" s="1"/>
     </row>
     <row r="38" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -2585,9 +2589,9 @@
       <c r="AB38" s="1"/>
     </row>
     <row r="39" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -2615,9 +2619,9 @@
       <c r="AB39" s="1"/>
     </row>
     <row r="40" spans="1:28" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
       <c r="D40" s="1"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -2645,9 +2649,9 @@
       <c r="AB40" s="1"/>
     </row>
     <row r="41" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -2821,6 +2825,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A34:C36"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C4"/>
+    <mergeCell ref="A6:C8"/>
+    <mergeCell ref="A10:C12"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A38:C40"/>
     <mergeCell ref="A5:C5"/>
@@ -2837,11 +2846,6 @@
     <mergeCell ref="A22:C24"/>
     <mergeCell ref="A26:C28"/>
     <mergeCell ref="A30:C32"/>
-    <mergeCell ref="A34:C36"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C4"/>
-    <mergeCell ref="A6:C8"/>
-    <mergeCell ref="A10:C12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
